--- a/data/outputSpecialityRpt/File1/RPT_RPT4414865920010NC_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT4414865920010NC_outputSpecialityRpt.xlsx
@@ -886,7 +886,7 @@
         <v>0.04260280017016599</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.03873219153964232</v>
+        <v>0.03873219153964231</v>
       </c>
       <c r="M15" s="14" t="n">
         <v>0.03494223177963598</v>
@@ -1026,7 +1026,7 @@
         <v>2.163073447707928</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>2.155524831820069</v>
+        <v>2.155524831820068</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>2.248922839922391</v>
@@ -1306,7 +1306,7 @@
         <v>13.32613157366968</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>9.100929288449654</v>
+        <v>9.100929288449652</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>6.573069012630077</v>
@@ -1446,7 +1446,7 @@
         <v>1.211466506697243</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.8273572080408778</v>
+        <v>0.8273572080408776</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>0.5975517284209161</v>
@@ -1726,7 +1726,7 @@
         <v>3.351683426294193</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>3.461752815092992</v>
+        <v>3.461752815092991</v>
       </c>
       <c r="M21" s="14" t="n">
         <v>3.541101334306325</v>
@@ -2006,7 +2006,7 @@
         <v>1.215554285764353</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>1.2125838768611</v>
+        <v>1.212583876861099</v>
       </c>
       <c r="M23" s="14" t="n">
         <v>1.206191964056825</v>
@@ -2146,7 +2146,7 @@
         <v>3.414304880822506</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>3.564453883187485</v>
+        <v>3.564453883187484</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>3.713591846412171</v>
@@ -2286,7 +2286,7 @@
         <v>2.266551844799974</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>2.063369018015644</v>
+        <v>2.063369018015645</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>1.856316765126961</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$14405.299126549819</t>
+          <t>$14405.29912654982</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$201451.5601484315</t>
+          <t>$201451.56014843154</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$3755.1431996238916</t>
+          <t>$3755.143199623892</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>5.012758572401599</v>
+        <v>5.0127585724016</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>8.26329562419226</v>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$195254.75578953212</t>
+          <t>$195254.75578953215</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$16271.229649127677</t>
+          <t>$16271.22964912768</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$15290.31763977193</t>
+          <t>$15290.317639771933</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
